--- a/StructureDefinition-ng-bundle-hospital-to-hmo.xlsx
+++ b/StructureDefinition-ng-bundle-hospital-to-hmo.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://dhin.org/2025Connectathon/StructureDefinition/ng-bundle-hospital-to-hmo</t>
+    <t>https://www.dhin-hie.org/IGs/StructureDefinition/ng-bundle-hospital-to-hmo</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-02T14:19:18+01:00</t>
+    <t>2025-09-10T08:54:29+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1016,7 +1016,7 @@
 Preauthorization RequestPredetermination Request</t>
   </si>
   <si>
-    <t xml:space="preserve">Claim {https://dhin.org/2025Connectathon/StructureDefinition/ng-claim}
+    <t xml:space="preserve">Claim {https://www.dhin-hie.org/IGs/StructureDefinition/ng-claim}
 </t>
   </si>
   <si>
@@ -1135,7 +1135,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Patient {https://dhin.org/2025Connectathon/StructureDefinition/NgPatient}
+    <t xml:space="preserve">Patient {https://www.dhin-hie.org/IGs/StructureDefinition/NgPatient}
 </t>
   </si>
   <si>
@@ -1250,7 +1250,7 @@
     <t>Bundle.entry:coverage.resource</t>
   </si>
   <si>
-    <t xml:space="preserve">Coverage {https://dhin.org/2025Connectathon/StructureDefinition/ng-claim-coverage}
+    <t xml:space="preserve">Coverage {https://www.dhin-hie.org/IGs/StructureDefinition/ng-claim-coverage}
 </t>
   </si>
   <si>
@@ -1369,7 +1369,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Encounter {https://dhin.org/2025Connectathon/StructureDefinition/ng-claim-encounter}
+    <t xml:space="preserve">Encounter {https://www.dhin-hie.org/IGs/StructureDefinition/ng-claim-encounter}
 </t>
   </si>
   <si>
@@ -1481,7 +1481,7 @@
     <t>Bundle.entry:procedure.resource</t>
   </si>
   <si>
-    <t xml:space="preserve">Procedure {https://dhin.org/2025Connectathon/StructureDefinition/ng-claim-procedure}
+    <t xml:space="preserve">Procedure {https://www.dhin-hie.org/IGs/StructureDefinition/ng-claim-procedure}
 </t>
   </si>
   <si>
@@ -1597,7 +1597,7 @@
 MeasurementResultsTests</t>
   </si>
   <si>
-    <t xml:space="preserve">Observation {https://dhin.org/2025Connectathon/StructureDefinition/ng-claim-observation}
+    <t xml:space="preserve">Observation {https://www.dhin-hie.org/IGs/StructureDefinition/ng-claim-observation}
 </t>
   </si>
   <si>
@@ -1718,7 +1718,7 @@
     <t>Bundle.entry:organization.resource</t>
   </si>
   <si>
-    <t xml:space="preserve">Organization {https://dhin.org/2025Connectathon/StructureDefinition/ng-imm-organization}
+    <t xml:space="preserve">Organization {https://www.dhin-hie.org/IGs/StructureDefinition/ng-imm-organization}
 </t>
   </si>
   <si>
@@ -1833,7 +1833,7 @@
     <t>Bundle.entry:practitioner.resource</t>
   </si>
   <si>
-    <t xml:space="preserve">Practitioner {https://dhin.org/2025Connectathon/StructureDefinition/NgPractitioner}
+    <t xml:space="preserve">Practitioner {https://www.dhin-hie.org/IGs/StructureDefinition/NgPractitioner}
 </t>
   </si>
   <si>
@@ -1948,7 +1948,7 @@
     <t>Bundle.entry:invoice.resource</t>
   </si>
   <si>
-    <t xml:space="preserve">Invoice {https://dhin.org/2025Connectathon/StructureDefinition/ng-claim-invoice}
+    <t xml:space="preserve">Invoice {https://www.dhin-hie.org/IGs/StructureDefinition/ng-claim-invoice}
 </t>
   </si>
   <si>
@@ -2393,7 +2393,7 @@
     <col min="8" max="8" width="12.6875" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="10.51171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="73.66015625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="68.74609375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
